--- a/public/templates/process-docs/通讯系统设备安装分部工程质量验收评定表.xlsx
+++ b/public/templates/process-docs/通讯系统设备安装分部工程质量验收评定表.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">工程编号：</t>
   </si>
   <si>
-    <t xml:space="preserve">5028G01-SG-ZHHC-AZ-006</t>
+    <t xml:space="preserve">{{文件编号}}</t>
   </si>
   <si>
     <t xml:space="preserve">表号：</t>
